--- a/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
+++ b/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/Documents/Work/Communications/Workshops/2022-08-16 CE-QUAL-W2 Workshop/_Agenda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/GitHub/environmentalsystems/CE-QUAL-W2/workshop/2022/Agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C1040A-2882-E745-9FA2-C83CD0DA3CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68099EEE-23CE-2D43-B31A-E840C9FEC92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5524DC16-E37C-514A-B687-063004997C4D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
   <si>
     <t>Todd</t>
   </si>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>-- BREAK --</t>
-  </si>
-  <si>
-    <t>Isaac &amp; Todd</t>
-  </si>
-  <si>
-    <t>Todd &amp; Isaac</t>
-  </si>
-  <si>
-    <t>Todd &amp; Lauren</t>
   </si>
   <si>
     <t>Isaac</t>
@@ -237,6 +228,12 @@
   </si>
   <si>
     <t>3.05 Workshop - Special Topics</t>
+  </si>
+  <si>
+    <t>Zhong &amp; Lauren</t>
+  </si>
+  <si>
+    <t>Zhong &amp; Isaac</t>
   </si>
 </sst>
 </file>
@@ -745,55 +742,55 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -853,50 +850,50 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1229,7 +1226,7 @@
     <col min="2" max="2" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="1.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="38.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" style="34" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" style="34" customWidth="1"/>
     <col min="8" max="8" width="38.83203125" style="1" customWidth="1"/>
@@ -1241,62 +1238,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="A1" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
     </row>
     <row r="3" spans="1:9" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="48"/>
+      <c r="A3" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="90"/>
       <c r="C3" s="34"/>
-      <c r="D3" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="48"/>
+      <c r="D3" s="90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:9" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1307,22 +1304,22 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,11 +1329,11 @@
       <c r="B6" s="2">
         <v>0.375</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="83"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="30"/>
-      <c r="H6" s="79"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="20"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1347,16 +1344,16 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="82" t="s">
-        <v>8</v>
+      <c r="F7" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>5</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="20"/>
@@ -1368,13 +1365,13 @@
       <c r="B8" s="2">
         <v>0.39583333333333298</v>
       </c>
-      <c r="D8" s="83"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="28"/>
-      <c r="F8" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="90" t="s">
-        <v>8</v>
+      <c r="F8" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="54" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="18"/>
       <c r="I8" s="20"/>
@@ -1386,18 +1383,18 @@
       <c r="B9" s="2">
         <v>0.40625</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="45" t="s">
+      <c r="E9" s="58"/>
+      <c r="F9" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="45" t="s">
+      <c r="G9" s="58"/>
+      <c r="H9" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="43"/>
+      <c r="I9" s="58"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -1407,22 +1404,22 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="81" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="82" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1432,19 +1429,19 @@
       <c r="B11" s="2">
         <v>0.42708333333333298</v>
       </c>
-      <c r="D11" s="80"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="28"/>
       <c r="F11" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1455,15 +1452,15 @@
         <v>0.4375</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="81" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="46" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="12"/>
@@ -1476,18 +1473,18 @@
       <c r="B13" s="2">
         <v>0.44791666666666702</v>
       </c>
-      <c r="D13" s="80"/>
+      <c r="D13" s="44"/>
       <c r="E13" s="28"/>
-      <c r="F13" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="90" t="s">
+      <c r="F13" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="43"/>
+      <c r="I13" s="58"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1496,19 +1493,19 @@
       <c r="B14" s="2">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="45" t="s">
+      <c r="E14" s="89"/>
+      <c r="F14" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="91" t="s">
-        <v>46</v>
+      <c r="G14" s="58"/>
+      <c r="H14" s="55" t="s">
+        <v>43</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1519,18 +1516,18 @@
         <v>0.46875</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="92"/>
+        <v>7</v>
+      </c>
+      <c r="H15" s="56"/>
       <c r="I15" s="21"/>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1540,12 +1537,12 @@
       <c r="B16" s="2">
         <v>0.47916666666666702</v>
       </c>
-      <c r="D16" s="80"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="28"/>
-      <c r="F16" s="83"/>
+      <c r="F16" s="47"/>
       <c r="G16" s="30"/>
       <c r="H16" s="26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>3</v>
@@ -1559,19 +1556,19 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>3</v>
@@ -1585,7 +1582,7 @@
         <v>0.5</v>
       </c>
       <c r="D18" s="12"/>
-      <c r="E18" s="87"/>
+      <c r="E18" s="51"/>
       <c r="F18" s="23"/>
       <c r="G18" s="33"/>
       <c r="H18" s="12"/>
@@ -1598,18 +1595,18 @@
       <c r="B19" s="2">
         <v>0.51041666666666696</v>
       </c>
-      <c r="D19" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="52"/>
-      <c r="H19" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="52"/>
+      <c r="D19" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="92"/>
+      <c r="F19" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="79"/>
+      <c r="H19" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="79"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1618,12 +1615,12 @@
       <c r="B20" s="2">
         <v>0.52083333333333304</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="54"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1632,12 +1629,12 @@
       <c r="B21" s="2">
         <v>0.53125</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="54"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1646,12 +1643,12 @@
       <c r="B22" s="2">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="54"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1660,12 +1657,12 @@
       <c r="B23" s="2">
         <v>0.55208333333333304</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="54"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -1674,12 +1671,12 @@
       <c r="B24" s="2">
         <v>0.5625</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="56"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="83"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
@@ -1689,22 +1686,22 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1714,11 +1711,11 @@
       <c r="B26" s="2">
         <v>0.58333333333333304</v>
       </c>
-      <c r="D26" s="83"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="30"/>
-      <c r="F26" s="84"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="39"/>
-      <c r="H26" s="85"/>
+      <c r="H26" s="49"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1729,16 +1726,16 @@
         <v>0.59375</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="37"/>
       <c r="I27" s="14"/>
@@ -1764,18 +1761,18 @@
       <c r="B29" s="2">
         <v>0.61458333333333304</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="45" t="s">
+      <c r="E29" s="58"/>
+      <c r="F29" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="42" t="s">
+      <c r="G29" s="58"/>
+      <c r="H29" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="43"/>
+      <c r="I29" s="58"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -1785,19 +1782,19 @@
         <v>0.625</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>2</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>0</v>
@@ -1810,11 +1807,11 @@
       <c r="B31" s="2">
         <v>0.63541666666666696</v>
       </c>
-      <c r="D31" s="83"/>
+      <c r="D31" s="47"/>
       <c r="E31" s="30"/>
-      <c r="F31" s="86"/>
+      <c r="F31" s="50"/>
       <c r="G31" s="30"/>
-      <c r="H31" s="85"/>
+      <c r="H31" s="49"/>
       <c r="I31" s="14"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1825,13 +1822,13 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>2</v>
@@ -1850,10 +1847,10 @@
       <c r="E33" s="33"/>
       <c r="F33" s="12"/>
       <c r="G33" s="15"/>
-      <c r="H33" s="42" t="s">
+      <c r="H33" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="I33" s="43"/>
+      <c r="I33" s="58"/>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
@@ -1862,14 +1859,14 @@
       <c r="B34" s="2">
         <v>0.66666666666666696</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="43"/>
-      <c r="F34" s="45" t="s">
+      <c r="E34" s="58"/>
+      <c r="F34" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="43"/>
+      <c r="G34" s="58"/>
       <c r="H34" s="31" t="s">
         <v>1</v>
       </c>
@@ -1885,19 +1882,19 @@
         <v>0.67708333333333404</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>0</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I35" s="19" t="s">
         <v>0</v>
@@ -1926,7 +1923,7 @@
       <c r="B38" s="5"/>
       <c r="C38" s="7"/>
       <c r="H38" s="61" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I38" s="61"/>
     </row>
@@ -1935,12 +1932,12 @@
       <c r="B39" s="6"/>
       <c r="C39" s="8"/>
       <c r="D39" s="62" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E39" s="63"/>
       <c r="F39" s="34"/>
       <c r="H39" s="68" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I39" s="69"/>
     </row>
@@ -1949,7 +1946,7 @@
       <c r="D40" s="64"/>
       <c r="E40" s="65"/>
       <c r="H40" s="70" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I40" s="71"/>
     </row>
@@ -1958,7 +1955,7 @@
       <c r="D41" s="64"/>
       <c r="E41" s="65"/>
       <c r="H41" s="72" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I41" s="73"/>
     </row>
@@ -1966,16 +1963,16 @@
       <c r="A42" s="2"/>
       <c r="D42" s="64"/>
       <c r="E42" s="65"/>
-      <c r="H42" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="58"/>
+      <c r="H42" s="84" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="85"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D43" s="64"/>
       <c r="E43" s="65"/>
       <c r="H43" s="59" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I43" s="60"/>
     </row>
@@ -1983,7 +1980,7 @@
       <c r="D44" s="64"/>
       <c r="E44" s="65"/>
       <c r="H44" s="74" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I44" s="75"/>
     </row>
@@ -1991,12 +1988,25 @@
       <c r="D45" s="66"/>
       <c r="E45" s="67"/>
       <c r="H45" s="76" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I45" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D19:E24"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H43:I43"/>
@@ -2013,22 +2023,9 @@
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D19:E24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="69" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="68" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
+++ b/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/GitHub/environmentalsystems/CE-QUAL-W2/workshop/2022/Agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68099EEE-23CE-2D43-B31A-E840C9FEC92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4A714D-AB60-2B4F-AC63-C7BB3F9156DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5524DC16-E37C-514A-B687-063004997C4D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="62">
   <si>
     <t>Todd</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Isaac</t>
-  </si>
-  <si>
-    <t>Barry &amp; Isaac</t>
   </si>
   <si>
     <t>Barry</t>
@@ -131,9 +128,6 @@
     <t>Course Closeout</t>
   </si>
   <si>
-    <t>Isaac &amp; Barry</t>
-  </si>
-  <si>
     <t>1.09 Lecture - Model Grid</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
   </si>
   <si>
     <t>Zhong &amp; Lauren</t>
-  </si>
-  <si>
-    <t>Zhong &amp; Isaac</t>
   </si>
 </sst>
 </file>
@@ -787,10 +778,31 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -872,27 +884,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1238,62 +1229,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
+      <c r="A1" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="3" spans="1:9" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="90"/>
+      <c r="A3" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="63"/>
       <c r="C3" s="34"/>
-      <c r="D3" s="90" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90" t="s">
+      <c r="D3" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90" t="s">
+      <c r="E3" s="63"/>
+      <c r="F3" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="90"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:9" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1304,22 +1295,22 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1344,13 +1335,13 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7" s="46" t="s">
         <v>5</v>
@@ -1368,7 +1359,7 @@
       <c r="D8" s="47"/>
       <c r="E8" s="28"/>
       <c r="F8" s="53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G8" s="54" t="s">
         <v>5</v>
@@ -1383,15 +1374,15 @@
       <c r="B9" s="2">
         <v>0.40625</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="60" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="58"/>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="60" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="58"/>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="60" t="s">
         <v>4</v>
       </c>
       <c r="I9" s="58"/>
@@ -1404,22 +1395,22 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1432,16 +1423,16 @@
       <c r="D11" s="44"/>
       <c r="E11" s="28"/>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1452,13 +1443,13 @@
         <v>0.4375</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G12" s="46" t="s">
         <v>3</v>
@@ -1476,12 +1467,12 @@
       <c r="D13" s="44"/>
       <c r="E13" s="28"/>
       <c r="F13" s="53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G13" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="60" t="s">
         <v>4</v>
       </c>
       <c r="I13" s="58"/>
@@ -1493,19 +1484,19 @@
       <c r="B14" s="2">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="57" t="s">
+      <c r="E14" s="62"/>
+      <c r="F14" s="60" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="58"/>
       <c r="H14" s="55" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1516,16 +1507,16 @@
         <v>0.46875</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H15" s="56"/>
       <c r="I15" s="21"/>
@@ -1542,7 +1533,7 @@
       <c r="F16" s="47"/>
       <c r="G16" s="30"/>
       <c r="H16" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>3</v>
@@ -1556,19 +1547,19 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>3</v>
@@ -1595,18 +1586,18 @@
       <c r="B19" s="2">
         <v>0.51041666666666696</v>
       </c>
-      <c r="D19" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="92"/>
-      <c r="F19" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="79"/>
-      <c r="H19" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="79"/>
+      <c r="D19" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="65"/>
+      <c r="F19" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="86"/>
+      <c r="H19" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="86"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1615,12 +1606,12 @@
       <c r="B20" s="2">
         <v>0.52083333333333304</v>
       </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="81"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="88"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1629,12 +1620,12 @@
       <c r="B21" s="2">
         <v>0.53125</v>
       </c>
-      <c r="D21" s="91"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="88"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1643,12 +1634,12 @@
       <c r="B22" s="2">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D22" s="91"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="88"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1657,12 +1648,12 @@
       <c r="B23" s="2">
         <v>0.55208333333333304</v>
       </c>
-      <c r="D23" s="91"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="81"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="88"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -1671,12 +1662,12 @@
       <c r="B24" s="2">
         <v>0.5625</v>
       </c>
-      <c r="D24" s="91"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="83"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="90"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
@@ -1686,22 +1677,22 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1726,13 +1717,13 @@
         <v>0.59375</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>0</v>
@@ -1761,15 +1752,15 @@
       <c r="B29" s="2">
         <v>0.61458333333333304</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="60" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="58"/>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="60" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="58"/>
-      <c r="H29" s="86" t="s">
+      <c r="H29" s="57" t="s">
         <v>4</v>
       </c>
       <c r="I29" s="58"/>
@@ -1782,19 +1773,19 @@
         <v>0.625</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E30" s="29" t="s">
         <v>0</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>2</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>0</v>
@@ -1822,13 +1813,13 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>2</v>
@@ -1847,7 +1838,7 @@
       <c r="E33" s="33"/>
       <c r="F33" s="12"/>
       <c r="G33" s="15"/>
-      <c r="H33" s="86" t="s">
+      <c r="H33" s="57" t="s">
         <v>4</v>
       </c>
       <c r="I33" s="58"/>
@@ -1859,11 +1850,11 @@
       <c r="B34" s="2">
         <v>0.66666666666666696</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="60" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="58"/>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="60" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="58"/>
@@ -1882,19 +1873,19 @@
         <v>0.67708333333333404</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>0</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G35" s="52" t="s">
         <v>0</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I35" s="19" t="s">
         <v>0</v>
@@ -1922,78 +1913,91 @@
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="7"/>
-      <c r="H38" s="61" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="61"/>
+      <c r="H38" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="68"/>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="63"/>
+      <c r="D39" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="70"/>
       <c r="F39" s="34"/>
-      <c r="H39" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="69"/>
+      <c r="H39" s="75" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="76"/>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="65"/>
-      <c r="H40" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="I40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="72"/>
+      <c r="H40" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="78"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="65"/>
-      <c r="H41" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="I41" s="73"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="72"/>
+      <c r="H41" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" s="80"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="65"/>
-      <c r="H42" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="I42" s="85"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="72"/>
+      <c r="H42" s="91" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="92"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="64"/>
-      <c r="E43" s="65"/>
-      <c r="H43" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="60"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="72"/>
+      <c r="H43" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="67"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="64"/>
-      <c r="E44" s="65"/>
-      <c r="H44" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="75"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="72"/>
+      <c r="H44" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="82"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="66"/>
-      <c r="E45" s="67"/>
-      <c r="H45" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="77"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="74"/>
+      <c r="H45" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D39:E45"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="D9:E9"/>
@@ -2009,20 +2013,7 @@
     <mergeCell ref="D19:E24"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D39:E45"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
     <mergeCell ref="F19:G24"/>
-    <mergeCell ref="H19:I24"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
+++ b/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/GitHub/environmentalsystems/CE-QUAL-W2/workshop/2022/Agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4A714D-AB60-2B4F-AC63-C7BB3F9156DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD21511F-ED85-8243-8FC8-3464A7E2427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5524DC16-E37C-514A-B687-063004997C4D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
   <si>
     <t>Todd</t>
   </si>
@@ -170,30 +170,6 @@
     <t>2.01 Lecture - Model Output</t>
   </si>
   <si>
-    <t>2.02 Lecture 2.1 - Water Temperature</t>
-  </si>
-  <si>
-    <t>2.03 Case Study 2.1 - Water Temperature</t>
-  </si>
-  <si>
-    <t>2.04 Lecture - Dissolved Oxygen</t>
-  </si>
-  <si>
-    <t>2.05 Case Study - Dissolved Oxygen</t>
-  </si>
-  <si>
-    <t>2.06 Lecture - Total Dissolved Gas</t>
-  </si>
-  <si>
-    <t>2.07 Case Study - Total Dissolved Gas</t>
-  </si>
-  <si>
-    <t>2.08 Lecture - Model Setup II</t>
-  </si>
-  <si>
-    <t>2.09 Case Study - Model Setup II</t>
-  </si>
-  <si>
     <t>2.10 Lecture - Model Utilities</t>
   </si>
   <si>
@@ -225,6 +201,33 @@
   </si>
   <si>
     <t>Zhong &amp; Lauren</t>
+  </si>
+  <si>
+    <t>Todd &amp; Lauren</t>
+  </si>
+  <si>
+    <t>2.02 Lecture - Model Setup II</t>
+  </si>
+  <si>
+    <t>2.03 Case Study - Model Setup II</t>
+  </si>
+  <si>
+    <t>2.04 Lecture 2.1 - Water Temperature</t>
+  </si>
+  <si>
+    <t>2.05 Case Study 2.1 - Water Temperature</t>
+  </si>
+  <si>
+    <t>2.06 Lecture - Dissolved Oxygen</t>
+  </si>
+  <si>
+    <t>2.07 Case Study - Dissolved Oxygen</t>
+  </si>
+  <si>
+    <t>2.08 Lecture - Total Dissolved Gas</t>
+  </si>
+  <si>
+    <t>2.09 Case Study - Total Dissolved Gas</t>
   </si>
 </sst>
 </file>
@@ -778,18 +781,15 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,12 +797,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -884,6 +878,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1222,43 +1225,40 @@
     <col min="7" max="7" width="12.83203125" style="34" customWidth="1"/>
     <col min="8" max="8" width="38.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" style="34" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="24"/>
-    <col min="11" max="11" width="29" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="24"/>
+    <col min="10" max="16384" width="8.83203125" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="3" spans="1:9" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="63"/>
+      <c r="B3" s="62"/>
       <c r="C3" s="34"/>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63" t="s">
+      <c r="E3" s="62"/>
+      <c r="F3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63" t="s">
+      <c r="G3" s="62"/>
+      <c r="H3" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="63"/>
+      <c r="I3" s="62"/>
     </row>
     <row r="4" spans="1:9" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1340,10 +1340,10 @@
       <c r="E7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="46" t="s">
+      <c r="F7" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="18"/>
@@ -1358,12 +1358,8 @@
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="28"/>
-      <c r="F8" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>5</v>
-      </c>
+      <c r="F8" s="47"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="18"/>
       <c r="I8" s="20"/>
     </row>
@@ -1374,18 +1370,18 @@
       <c r="B9" s="2">
         <v>0.40625</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="60" t="s">
+      <c r="E9" s="59"/>
+      <c r="F9" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="58"/>
-      <c r="H9" s="60" t="s">
+      <c r="G9" s="59"/>
+      <c r="H9" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="58"/>
+      <c r="I9" s="59"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -1398,16 +1394,16 @@
         <v>34</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I10" s="46" t="s">
         <v>6</v>
@@ -1422,14 +1418,10 @@
       </c>
       <c r="D11" s="44"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>6</v>
-      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>6</v>
@@ -1449,10 +1441,10 @@
         <v>6</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="15"/>
@@ -1467,15 +1459,15 @@
       <c r="D13" s="44"/>
       <c r="E13" s="28"/>
       <c r="F13" s="53" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="H13" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="58"/>
+      <c r="I13" s="59"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1484,14 +1476,14 @@
       <c r="B14" s="2">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D14" s="61" t="s">
+      <c r="D14" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="60" t="s">
+      <c r="E14" s="61"/>
+      <c r="F14" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="58"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="55" t="s">
         <v>41</v>
       </c>
@@ -1512,11 +1504,11 @@
       <c r="E15" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>5</v>
+      <c r="F15" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>6</v>
       </c>
       <c r="H15" s="56"/>
       <c r="I15" s="21"/>
@@ -1530,10 +1522,14 @@
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="28"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>6</v>
+      </c>
       <c r="H16" s="26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>3</v>
@@ -1552,14 +1548,14 @@
       <c r="E17" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>3</v>
@@ -1574,8 +1570,12 @@
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="51"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="33"/>
+      <c r="F18" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>3</v>
+      </c>
       <c r="H18" s="12"/>
       <c r="I18" s="15"/>
     </row>
@@ -1586,18 +1586,18 @@
       <c r="B19" s="2">
         <v>0.51041666666666696</v>
       </c>
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="65"/>
-      <c r="F19" s="85" t="s">
+      <c r="E19" s="92"/>
+      <c r="F19" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="86"/>
-      <c r="H19" s="85" t="s">
+      <c r="G19" s="83"/>
+      <c r="H19" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="86"/>
+      <c r="I19" s="83"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1606,12 +1606,12 @@
       <c r="B20" s="2">
         <v>0.52083333333333304</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1620,12 +1620,12 @@
       <c r="B21" s="2">
         <v>0.53125</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="88"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1634,12 +1634,12 @@
       <c r="B22" s="2">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="87"/>
-      <c r="I22" s="88"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1648,12 +1648,12 @@
       <c r="B23" s="2">
         <v>0.55208333333333304</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -1662,12 +1662,12 @@
       <c r="B24" s="2">
         <v>0.5625</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="90"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="87"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
@@ -1683,13 +1683,13 @@
         <v>6</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>7</v>
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>0</v>
@@ -1752,18 +1752,18 @@
       <c r="B29" s="2">
         <v>0.61458333333333304</v>
       </c>
-      <c r="D29" s="60" t="s">
+      <c r="D29" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="60" t="s">
+      <c r="E29" s="59"/>
+      <c r="F29" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="58"/>
-      <c r="H29" s="57" t="s">
+      <c r="G29" s="59"/>
+      <c r="H29" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="58"/>
+      <c r="I29" s="59"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -1776,16 +1776,16 @@
         <v>29</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>2</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         <v>38</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>2</v>
@@ -1838,10 +1838,10 @@
       <c r="E33" s="33"/>
       <c r="F33" s="12"/>
       <c r="G33" s="15"/>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="I33" s="58"/>
+      <c r="I33" s="59"/>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
@@ -1850,14 +1850,14 @@
       <c r="B34" s="2">
         <v>0.66666666666666696</v>
       </c>
-      <c r="D34" s="60" t="s">
+      <c r="D34" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="58"/>
-      <c r="F34" s="60" t="s">
+      <c r="E34" s="59"/>
+      <c r="F34" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="58"/>
+      <c r="G34" s="59"/>
       <c r="H34" s="31" t="s">
         <v>1</v>
       </c>
@@ -1913,75 +1913,75 @@
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="7"/>
-      <c r="H38" s="68" t="s">
+      <c r="H38" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="68"/>
+      <c r="I38" s="65"/>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="69" t="s">
+      <c r="D39" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="70"/>
+      <c r="E39" s="67"/>
       <c r="F39" s="34"/>
-      <c r="H39" s="75" t="s">
+      <c r="H39" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="76"/>
+      <c r="I39" s="73"/>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="72"/>
-      <c r="H40" s="77" t="s">
+      <c r="D40" s="68"/>
+      <c r="E40" s="69"/>
+      <c r="H40" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="78"/>
+      <c r="I40" s="75"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="72"/>
-      <c r="H41" s="79" t="s">
+      <c r="D41" s="68"/>
+      <c r="E41" s="69"/>
+      <c r="H41" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="80"/>
+      <c r="I41" s="77"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="72"/>
-      <c r="H42" s="91" t="s">
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
+      <c r="H42" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="I42" s="92"/>
+      <c r="I42" s="89"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="71"/>
-      <c r="E43" s="72"/>
-      <c r="H43" s="66" t="s">
+      <c r="D43" s="68"/>
+      <c r="E43" s="69"/>
+      <c r="H43" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="67"/>
+      <c r="I43" s="64"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="71"/>
-      <c r="E44" s="72"/>
-      <c r="H44" s="81" t="s">
+      <c r="D44" s="68"/>
+      <c r="E44" s="69"/>
+      <c r="H44" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="82"/>
+      <c r="I44" s="79"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="73"/>
-      <c r="E45" s="74"/>
-      <c r="H45" s="83" t="s">
+      <c r="D45" s="70"/>
+      <c r="E45" s="71"/>
+      <c r="H45" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="84"/>
+      <c r="I45" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -1990,6 +1990,12 @@
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D19:E24"/>
+    <mergeCell ref="F19:G24"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="D39:E45"/>
@@ -1998,7 +2004,6 @@
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="H44:I44"/>
     <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H33:I33"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D14:E14"/>
@@ -2007,13 +2012,8 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D19:E24"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="F19:G24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
+++ b/workshop/2022/Agenda/CE-QUAL-W2_Workshop_Aug_2022_Agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/todd/GitHub/environmentalsystems/CE-QUAL-W2/workshop/2022/Agenda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD21511F-ED85-8243-8FC8-3464A7E2427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0294683D-98CF-BF4C-BF23-B74CD25203A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{5524DC16-E37C-514A-B687-063004997C4D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>Todd</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Discussion / Tours</t>
   </si>
   <si>
-    <t>Tour - Fish Flume</t>
-  </si>
-  <si>
     <t>Tour - Sediment Lab</t>
   </si>
   <si>
@@ -228,6 +225,18 @@
   </si>
   <si>
     <t>2.09 Case Study - Total Dissolved Gas</t>
+  </si>
+  <si>
+    <t>-- FIRE DRILL &amp; BREAK --</t>
+  </si>
+  <si>
+    <t>Tour - CEERF (Fish Flume):</t>
+  </si>
+  <si>
+    <t>Cognitive Environmental Effects Research Flume</t>
+  </si>
+  <si>
+    <t>3.04 Workshop - Upgrade to V4.5, continued</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -664,9 +673,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -721,12 +727,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -739,9 +739,6 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -775,12 +772,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -790,13 +790,19 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -883,11 +889,29 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1219,48 +1243,48 @@
     <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="1.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="34" customWidth="1"/>
-    <col min="8" max="8" width="38.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" style="34" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="24"/>
+    <col min="4" max="4" width="42.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="33" customWidth="1"/>
+    <col min="8" max="8" width="42.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" style="33" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-    </row>
-    <row r="3" spans="1:9" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="62" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+    </row>
+    <row r="3" spans="1:9" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62" t="s">
+      <c r="E3" s="57"/>
+      <c r="F3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="62"/>
-    </row>
-    <row r="4" spans="1:9" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I3" s="57"/>
+    </row>
+    <row r="4" spans="1:9" s="24" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -1268,19 +1292,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -1294,22 +1318,22 @@
       <c r="B5" s="2">
         <v>0.36458333333333331</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="29" t="s">
+      <c r="F5" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="28" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1320,11 +1344,13 @@
       <c r="B6" s="2">
         <v>0.375</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="51" t="s">
+        <v>64</v>
+      </c>
       <c r="I6" s="20"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1334,20 +1360,22 @@
       <c r="B7" s="2">
         <v>0.38541666666666702</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="29" t="s">
+      <c r="D7" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="20"/>
+      <c r="H7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
@@ -1356,11 +1384,11 @@
       <c r="B8" s="2">
         <v>0.39583333333333298</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="18"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="20"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1370,18 +1398,20 @@
       <c r="B9" s="2">
         <v>0.40625</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="58" t="s">
+      <c r="G9" s="56"/>
+      <c r="H9" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="59"/>
-      <c r="H9" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="59"/>
+      <c r="I9" s="56"/>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -1390,22 +1420,18 @@
       <c r="B10" s="2">
         <v>0.41666666666666702</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>5</v>
-      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="46" t="s">
+      <c r="H10" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="42" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1416,12 +1442,16 @@
       <c r="B11" s="2">
         <v>0.42708333333333298</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="33"/>
+      <c r="D11" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>6</v>
@@ -1434,16 +1464,12 @@
       <c r="B12" s="2">
         <v>0.4375</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="46" t="s">
+      <c r="D12" s="40"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="42" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="12"/>
@@ -1456,18 +1482,22 @@
       <c r="B13" s="2">
         <v>0.44791666666666702</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="54" t="s">
+      <c r="D13" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="56"/>
+      <c r="F13" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13" s="59"/>
+      <c r="H13" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -1476,20 +1506,20 @@
       <c r="B14" s="2">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="61"/>
-      <c r="F14" s="58" t="s">
+      <c r="G14" s="56"/>
+      <c r="H14" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="59"/>
-      <c r="H14" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>8</v>
-      </c>
+      <c r="I14" s="56"/>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -1498,20 +1528,20 @@
       <c r="B15" s="2">
         <v>0.46875</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="21"/>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -1520,20 +1550,20 @@
       <c r="B16" s="2">
         <v>0.47916666666666702</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="28"/>
+      <c r="D16" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>3</v>
+      </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>3</v>
-      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -1542,23 +1572,19 @@
       <c r="B17" s="2">
         <v>0.48958333333333298</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="46" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="42" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>50</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1568,16 +1594,18 @@
       <c r="B18" s="2">
         <v>0.5</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="54" t="s">
+      <c r="D18" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="91"/>
+      <c r="F18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="15"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="14"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -1586,18 +1614,16 @@
       <c r="B19" s="2">
         <v>0.51041666666666696</v>
       </c>
-      <c r="D19" s="91" t="s">
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="92"/>
-      <c r="F19" s="82" t="s">
+      <c r="G19" s="82"/>
+      <c r="H19" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="83"/>
-      <c r="H19" s="82" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="83"/>
+      <c r="I19" s="82"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
@@ -1606,12 +1632,12 @@
       <c r="B20" s="2">
         <v>0.52083333333333304</v>
       </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="85"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
@@ -1620,12 +1646,12 @@
       <c r="B21" s="2">
         <v>0.53125</v>
       </c>
-      <c r="D21" s="91"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="85"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="84"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1634,12 +1660,12 @@
       <c r="B22" s="2">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D22" s="91"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="85"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="84"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1648,12 +1674,12 @@
       <c r="B23" s="2">
         <v>0.55208333333333304</v>
       </c>
-      <c r="D23" s="91"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="85"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="84"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -1662,12 +1688,16 @@
       <c r="B24" s="2">
         <v>0.5625</v>
       </c>
-      <c r="D24" s="91"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="87"/>
+      <c r="D24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="86"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
@@ -1676,20 +1706,16 @@
       <c r="B25" s="2">
         <v>0.57291666666666696</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="29" t="s">
+      <c r="D25" s="12"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="28" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>7</v>
@@ -1702,12 +1728,16 @@
       <c r="B26" s="2">
         <v>0.58333333333333304</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="14"/>
+      <c r="D26" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
@@ -1716,20 +1746,20 @@
       <c r="B27" s="2">
         <v>0.59375</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H27" s="37"/>
-      <c r="I27" s="14"/>
+      <c r="H27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
@@ -1738,12 +1768,14 @@
       <c r="B28" s="2">
         <v>0.60416666666666696</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="33"/>
+      <c r="D28" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="56"/>
       <c r="F28" s="12"/>
       <c r="G28" s="15"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="15"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
@@ -1752,18 +1784,18 @@
       <c r="B29" s="2">
         <v>0.61458333333333304</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="59"/>
-      <c r="F29" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="59"/>
-      <c r="H29" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="59"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -1772,24 +1804,16 @@
       <c r="B30" s="2">
         <v>0.625</v>
       </c>
-      <c r="D30" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="29" t="s">
+      <c r="D30" s="22"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>0</v>
-      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
@@ -1798,12 +1822,18 @@
       <c r="B31" s="2">
         <v>0.63541666666666696</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="14"/>
+      <c r="D31" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="46"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="59"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
@@ -1812,20 +1842,20 @@
       <c r="B32" s="2">
         <v>0.64583333333333304</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>53</v>
-      </c>
+      <c r="D32" s="43"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="15"/>
+      <c r="H32" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
@@ -1834,14 +1864,14 @@
       <c r="B33" s="2">
         <v>0.65625</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="33"/>
+      <c r="D33" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="56"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="59"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="19"/>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
@@ -1850,20 +1880,18 @@
       <c r="B34" s="2">
         <v>0.66666666666666696</v>
       </c>
-      <c r="D34" s="58" t="s">
+      <c r="D34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="59"/>
-      <c r="F34" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="59"/>
-      <c r="H34" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>0</v>
-      </c>
+      <c r="G34" s="89"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="20"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
@@ -1872,22 +1900,18 @@
       <c r="B35" s="2">
         <v>0.67708333333333404</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="22"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="G35" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="F35" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="18" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1898,12 +1922,16 @@
       <c r="B36" s="2">
         <v>0.6875</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="21"/>
+      <c r="D36" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="F36" s="35"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="20"/>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
@@ -1913,89 +1941,87 @@
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="7"/>
-      <c r="H38" s="65" t="s">
+      <c r="H38" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="65"/>
+      <c r="I38" s="64"/>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="66" t="s">
+      <c r="D39" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="67"/>
-      <c r="F39" s="34"/>
-      <c r="H39" s="72" t="s">
+      <c r="E39" s="66"/>
+      <c r="F39" s="33"/>
+      <c r="H39" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="73"/>
+      <c r="I39" s="72"/>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="69"/>
-      <c r="H40" s="74" t="s">
+      <c r="D40" s="67"/>
+      <c r="E40" s="68"/>
+      <c r="H40" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="75"/>
+      <c r="I40" s="74"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="69"/>
-      <c r="H41" s="76" t="s">
+      <c r="D41" s="67"/>
+      <c r="E41" s="68"/>
+      <c r="H41" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="77"/>
+      <c r="I41" s="76"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69"/>
-      <c r="H42" s="88" t="s">
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="H42" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="I42" s="89"/>
+      <c r="I42" s="88"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="68"/>
-      <c r="E43" s="69"/>
-      <c r="H43" s="63" t="s">
+      <c r="D43" s="67"/>
+      <c r="E43" s="68"/>
+      <c r="H43" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="64"/>
+      <c r="I43" s="63"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="68"/>
-      <c r="E44" s="69"/>
-      <c r="H44" s="78" t="s">
+      <c r="D44" s="67"/>
+      <c r="E44" s="68"/>
+      <c r="H44" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="79"/>
+      <c r="I44" s="78"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="70"/>
-      <c r="E45" s="71"/>
-      <c r="H45" s="80" t="s">
+      <c r="D45" s="69"/>
+      <c r="E45" s="70"/>
+      <c r="H45" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="81"/>
+      <c r="I45" s="80"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="H19:I24"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="H29:I29"/>
+  <mergeCells count="28">
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D19:E24"/>
     <mergeCell ref="F19:G24"/>
+    <mergeCell ref="D18:E23"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="D39:E45"/>
@@ -2004,19 +2030,20 @@
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="H44:I44"/>
     <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D14:E14"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="68" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="63" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>